--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7258,6 +7258,3046 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>bouton_retour</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Retour</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Terug</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>bouton_continuer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Continuer</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Continue</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Doorgaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>bouton_ajouter</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Ajouter</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Add</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Toevoegen</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>bouton_ajouter_ligne</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Ajouter une ligne</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Add a row</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Rij toevoegen</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>bouton_enregistrer</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Enregistrer</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Opslaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>non_renseigne</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>non renseigné</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>not provided</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>niet ingevuld</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>label_version</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Versie</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>identification_titre</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Identification du chantier</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Site identification</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Identificatie van de bouwplaats</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>identification_sous_titre</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Nouveau chantier, ou reprise d'un RePSS déjà commencé</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>New site, or resuming an already-started RePSS</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Nieuwe bouwplaats, of een reeds gestart RePSS-document hervatten</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>identification_numero_chantier</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>N° chantier</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Site no.</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Bouwplaatsnr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>identification_pm_lead</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>PM lead (optionnel)</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Lead PM (optional)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Hoofd-PM (optioneel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>identification_pm_secondaire</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>PM secondaire (optionnel)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Secondary PM (optional)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Secundaire PM (optioneel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>identification_ou</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>ou</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>or</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>of</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>identification_reprendre_bouton</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Reprendre un RePSS existant (fichier .json)</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Resume an existing RePSS (.json file)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Een bestaand RePSS hervatten (.json-bestand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>identification_dossier_importe</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Dossier importé</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>File imported</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Bestand geïmporteerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>identification_version_mot</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>versie</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>identification_modifie_le</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>modifié le</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>modified on</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>gewijzigd op</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>identification_erreur_fichier</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Ce fichier ne semble pas être un dossier RePSS valide.</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>This file doesn't appear to be a valid RePSS file.</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Dit bestand lijkt geen geldig RePSS-dossier te zijn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>caracterisation_titre</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Caractérisation du chantier</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Site characterisation</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Karakterisering van de bouwplaats</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>caracterisation_question</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RePSS abrégé ou complet ?</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Abridged or full RePSS?</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Verkorte of volledige RePSS?</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>caracterisation_abrege</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Abrégé</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Abridged</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Verkort</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>caracterisation_complet</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Complet</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Volledig</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>caracterisation_abrege_indispo</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Abrégé non disponible : au moins un critère ci-dessous s'applique à ce chantier.</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Abridged not available: at least one of the criteria below applies to this site.</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Verkort niet beschikbaar: minstens één van onderstaande criteria is van toepassing op deze bouwplaats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>caracterisation_aide_intro</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Si l'un de ces points concerne le chantier, le complet est requis</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>If any of these points apply to the site, the full version is required</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Als een van deze punten van toepassing is op de bouwplaats, is de volledige versie vereist</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>caracterisation_critere_heures</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Heures de chantier &lt; 1000</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Site hours &lt; 1000</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Werfuren &lt; 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>caracterisation_critere_hauteur</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Travail en hauteur ≥ 5 m</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Work at height ≥ 5 m</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Werken op hoogte ≥ 5 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>caracterisation_critere_ht</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Haute tension</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>High voltage</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Hoogspanning</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>caracterisation_critere_confine</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Espace confiné</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Confined space</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Besloten ruimte</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>caracterisation_corps_metier</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Corps de métier concernés</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Trades involved</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Betrokken vakgroepen</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>infos_admin_titre</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Infos admin.</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Admin info</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Administratieve info</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>contacts_reference_titre</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Contacts de référence</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Reference contacts</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Referentiecontacten</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>roles_fixes_suffixe</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>rôles fixes</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>fixed roles</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>vaste rollen</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>version_dossier_titre</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Version du dossier</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>File version</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Versie van het dossier</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>derniere_modification</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Dernière modification</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Last modified</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Laatst gewijzigd</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>motif_nouvelle_version</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Motif de la nouvelle version (optionnel)</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Reason for the new version (optional)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Reden voor de nieuwe versie (optioneel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>contacts_urgence_titre</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Contacts d'urgence</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Emergency contacts</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Noodcontacten</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>n_interne_placeholder</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>N° interne (ex. GSK)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Internal no. (e.g. GSK)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Intern nr. (bv. GSK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>centre_antipoison_label</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Centre antipoison</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Poison control centre</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Antigifcentrum</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>police_label</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Politie</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>police_zone_proche</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Zone la plus proche</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Nearest zone</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Dichtstbijzijnde zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>titre_infos_chantier_usine</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Site &amp; plant info</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Info bouwplaats &amp; fabriek</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>site_seveso</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Site SEVESO</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>SEVESO site</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SEVESO-site</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>coactivite</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Coactivité avec le personnel client</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Co-activity with client staff</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Co-activiteit met personeel van de klant</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>accueil_securite_requis</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Accueil sécurité requis</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Safety induction required</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Veiligheidsonthaal vereist</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>presence_gaz</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Présence de gaz</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Presence of gas</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Aanwezigheid van gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>matieres_premieres_dangereuses</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Matières premières / produits dangereux</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Raw materials / hazardous products</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Grondstoffen / gevaarlijke producten</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>pressions_temperatures</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Pressions / températures particulières</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Specific pressures / temperatures</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Specifieke drukken / temperaturen</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>sanitaires</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Sanitaires</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Sanitary facilities</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Sanitair</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>vestiaires</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Vestiaires</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Changing rooms</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Kleedkamers</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>douches</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Infos chantier usine</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Douches</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Showers</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Douches</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>analyse_titre_complet</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Risk analysis</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Risicoanalyse</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>analyse_titre_abrege</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Risques &amp; mesures</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Risks &amp; measures</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Risico's &amp; maatregelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>analyse_compteur_selection</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>sélectionnée(s)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>selected</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>geselecteerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>analyse_aide_abrege</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Catalogue abrégé : coche les dangers présents sur le chantier.</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Abridged catalogue: tick the hazards present on the site.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Verkorte catalogus: vink de gevaren aan die aanwezig zijn op de bouwplaats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>analyse_aide_complet</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Filtré selon le corps de métier de ce chantier → coche les lignes de risque concernées.</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Filtered by this site's trades → tick the relevant risk lines.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Gefilterd op basis van de vakgroepen van deze bouwplaats → vink de relevante risicolijnen aan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>analyse_message_corps_metier</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Coche un corps de métier à l'étape précédente pour voir apparaître d'autres catégories.</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Tick a trade on the previous step to reveal more categories.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Vink een vakgroep aan in de vorige stap om meer categorieën te tonen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>analyse_non_couvert_abrege</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Non couvert par l'abrégé, nécessite le RePSS complet.</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Not covered by the abridged version, requires the full RePSS.</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Niet gedekt door de verkorte versie, vereist de volledige RePSS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>remarque_optionnelle_placeholder</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Remarque (optionnel)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Remark (optional)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Opmerking (optioneel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>moadr_titre</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Point hors catalogue (MOADR)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Point outside the catalogue (MOADR)</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Punt buiten de catalogus (MOADR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>moadr_aide</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Une situation spécifique au chantier n'est couverte par aucune ligne du catalogue ? Décris-la ici → elle sera traitée à part et jointe en annexe, sans bloquer la suite du dossier.</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>A site-specific situation isn't covered by any catalogue line? Describe it here → it will be handled separately and attached as an appendix, without blocking the rest of the file.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Een specifieke situatie op de bouwplaats wordt door geen enkele catalogusregel gedekt? Beschrijf ze hier → ze wordt apart behandeld en als bijlage toegevoegd, zonder de rest van het dossier te blokkeren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>moadr_placeholder</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Décrire la situation…</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Describe the situation…</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Beschrijf de situatie…</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>moadr_mention_document</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Ce point sera traité à part et joint en annexe.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>This point will be handled separately and attached as an appendix.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Dit punt wordt apart behandeld en als bijlage toegevoegd.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>moadr_demandes_en_attente</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>MOADR</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>demande(s) MOADR en attente</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>MOADR request(s) pending</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>MOADR-aanvra(a)g(en) in behandeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>genere_auto</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>généré automatiquement</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>generated automatically</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>automatisch gegenereerd</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>documents_auto_titre</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Documents automatiques</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Automatic documents</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Automatische documenten</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>emargement_label</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Émargement</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Sign-off sheet</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Aftekenlijst</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>grille_kinney_label</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Grille Kinney</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Kinney matrix</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Kinney-matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>fichier_joint</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Fichier joint</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Attached file</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Bijgevoegd bestand</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>notes_complementaires_placeholder</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Notes complémentaires</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Additional notes</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Aanvullende opmerkingen</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>langue_document_label</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Langue du document</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Document language</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Taal van het document</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>numero_repss_attribue</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Numéro RePSS attribué</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>RePSS number assigned</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>RePSS-nummer toegekend</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>enregistrer_json_bouton</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Enregistrer le .json</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Save the .json</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Het .json-bestand opslaan</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>generer_pdf_bouton</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Générer le PDF</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Generate the PDF</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>PDF genereren</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>generation_en_cours</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Génération…</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Generating…</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Bezig met genereren…</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>step_accueil</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Accueil</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>step_identification</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Identificatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>step_caracterisation</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Caractérisation</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Characterisation</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Karakterisering</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>step_infos_admin</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Infos admin.</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Admin info</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Administratieve info</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>step_infos_chantier_usine</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Site &amp; plant info</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Info bouwplaats &amp; fabriek</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>step_analyse_complet</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Risk analysis</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Risicoanalyse</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>step_analyse_abrege</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Risques &amp; mesures</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Risks &amp; measures</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Risico's &amp; maatregelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>step_generation_complet</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Annexes &amp; génération</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Appendices &amp; generation</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Bijlagen &amp; generatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>step_generation_abrege</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Génération</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Generation</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Generatie</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>comment_ca_marche</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Comment ça marche ?</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>How does it work?</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Hoe werkt het?</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>sidebar_info_text</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Télécharge l'état actuel dans un fichier .json à déposer dans le dossier SharePoint du chantier. Pour reprendre plus tard : reviens sur l'écran d'identification et clique "Reprendre un RePSS existant", puis choisis ce fichier.</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Downloads the current state as a .json file to place in the site's SharePoint folder. To resume later: go back to the identification screen and click "Resume an existing RePSS", then choose this file.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Downloadt de huidige status als een .json-bestand om in de SharePoint-map van de bouwplaats te plaatsen. Om later verder te gaan: keer terug naar het identificatiescherm en klik op "Een bestaand RePSS hervatten", en kies dan dit bestand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>tristate_interne</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Interne</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>tristate_client</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Klant</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>tristate_na</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>App - Général</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>N.A.</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>N.v.t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>reponse_au_pss</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Réponse au P.S.S.</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>PSS Response</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Antwoord op de PSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>repss_abrege_label</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>RePSS abrégé</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Abridged RePSS</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Verkorte RePSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>repss_complet_label</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>RePSS complet</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Full RePSS</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Volledige RePSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>moadr_section_titre_pdf</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Demandes MOADR en attente</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Pending MOADR requests</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>MOADR-aanvragen in behandeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>hopital_code_postal_placeholder</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Code postal du chantier</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Site postcode</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Postcode van de bouwplaats</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>hopital_saisis_code_postal</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Saisis le code postal du chantier pour une suggestion automatique.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Enter the site's postcode for an automatic suggestion.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Voer de postcode van de bouwplaats in voor een automatische suggestie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>hopital_ajouter_manuellement</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Ajouter un autre hôpital manuellement…</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Add another hospital manually…</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Handmatig een ander ziekenhuis toevoegen…</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G288"/>
+  <dimension ref="A1:G308"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10298,6 +10298,746 @@
         </is>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>page_explication_titre</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>À propos de ce document</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>About this document</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Over dit document</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>page_explication_texte</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Ce document constitue la réponse de l'entreprise au Plan de Sécurité et de Santé (P.S.S.) établi par le coordinateur sécurité pour ce chantier. Il décrit l'organisation, les mesures de prévention et les risques identifiés pour les travaux réalisés par vma sud. Il est généré automatiquement à partir des informations encodées par le chef de projet et doit être déposé dans le dossier SharePoint du chantier.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>This document constitutes the company's response to the Health and Safety Plan (H&amp;SP) established by the safety coordinator for this site. It describes the organisation, prevention measures and risks identified for the works carried out by vma sud. It is generated automatically from the information entered by the project manager and must be filed in the site's SharePoint folder.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Dit document vormt het antwoord van het bedrijf op het Veiligheids- en Gezondheidsplan (V&amp;G-plan) opgesteld door de veiligheidscoördinator voor deze werf. Het beschrijft de organisatie, de preventiemaatregelen en de geïdentificeerde risico's voor de werken uitgevoerd door vma sud. Het wordt automatisch gegenereerd op basis van de door de projectleider ingevoerde gegevens en moet in de SharePoint-map van de werf worden geplaatst.</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>table_matieres_titre</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Table des matières</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Table of contents</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Inhoudsopgave</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>carac_chantier_plan_installation</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Plan général d'installation à joindre.</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>General site layout plan to be attached.</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Algemeen inrichtingsplan bij te voegen.</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>carac_chantier_point_rassemblement</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Point de rassemblement identifié.</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Assembly point identified.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Verzamelpunt geïdentificeerd.</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>annexe_label</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Annexe</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Bijlage</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>annexe1_legende_kinney_titre</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Légende Kinney</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Kinney legend</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Kinney-legende</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>kinney_formule</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>R = Probabilité × Exposition × Gravité</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>R = Probability × Exposure × Severity</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>R = Waarschijnlijkheid × Blootstelling × Ernst</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>kinney_legende_intro</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>La méthode Kinney évalue chaque risque par le produit de trois facteurs. Le score obtenu détermine le niveau de risque et les mesures de prévention à prendre.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>The Kinney method assesses each risk by multiplying three factors. The resulting score determines the risk level and the prevention measures to be taken.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>De Kinney-methode beoordeelt elk risico aan de hand van het product van drie factoren. De bekomen score bepaalt het risiconiveau en de te nemen preventiemaatregelen.</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>evaluation_label</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Évaluation</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Assessment</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Beoordeling</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>evaluation_initiale_label</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Évaluation initiale</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Initial assessment</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Initiële beoordeling</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>evaluation_residuelle_label</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Évaluation résiduelle (après mesures)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Residual assessment (after measures)</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Residuele beoordeling (na maatregelen)</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>mesures_prevention_label</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Mesures de prévention</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Prevention measures</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Preventiemaatregelen</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>risque_col_ref</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Réf.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Ref.</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>risque_col_source_danger</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Sources de danger ou déviation</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Hazard sources or deviation</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Gevarenbronnen of afwijking</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>risque_col_risques</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Risques</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Risico's</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>tbl_nom</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Naam</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>tbl_email</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>tbl_tel</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Tél.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Tel.</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Tel.</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>niveau_risque_label</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Niveau de risque</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Risk level</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Risiconiveau</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Ajouté pour §12 PDF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G308"/>
+  <dimension ref="A1:G313"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11038,6 +11038,191 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>explication_bloc1_titre</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Objet du document</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Purpose of this document</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Doel van dit document</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Ajouté : restructuration page explication en 3 blocs</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>explication_bloc2_titre</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Obligation d'information</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Duty to inform</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Informatieplicht</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>Ajouté : restructuration page explication en 3 blocs</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>explication_bloc2_texte</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Ce document doit être porté à la connaissance de l'ensemble du personnel vma sud, des intérimaires et des sous-traitants intervenant sur ce chantier, dans le cadre de la procédure d'accueil et d'ouverture de chantier. Cette information est une obligation légale, préalable à toute intervention sur le site.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>This document must be brought to the attention of all vma sud staff, temporary workers and subcontractors working on this site, as part of the site induction and opening procedure. This information is a legal requirement, to be completed before any work begins on site.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Dit document moet ter kennis worden gebracht van alle vma sud-personeelsleden, uitzendkrachten en onderaannemers die op deze werf actief zijn, in het kader van de onthaal- en openingsprocedure van de werf. Deze informatieverstrekking is een wettelijke verplichting, voorafgaand aan elke interventie op de werf.</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Ajouté : restructuration page explication en 3 blocs</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>explication_bloc3_titre</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Dépôt et prise de connaissance</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Filing and acknowledgement</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Indiening en kennisname</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Ajouté : restructuration page explication en 3 blocs</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>explication_bloc3_texte</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Ce document doit être déposé dans le dossier SharePoint du chantier. La prise de connaissance par chaque intervenant doit être enregistrée par signature sur la page « Émargement » en fin de document.</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>This document must be filed in the site's SharePoint folder. Acknowledgement of having read it must be recorded by each person's signature on the “Attendance sheet” (Émargement) page at the end of the document.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Dit document moet worden geplaatst in de SharePoint-map van de werf. De kennisname door elke betrokkene moet worden vastgelegd door een handtekening op de pagina 'Aanwezigheidslijst' (Émargement) aan het einde van het document.</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Ajouté : restructuration page explication en 3 blocs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G313"/>
+  <dimension ref="A1:G320"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11223,6 +11223,265 @@
         </is>
       </c>
     </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>adresse_rue</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Rens.gen.</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Rue</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Street</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Straat</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Ajouté : scission adresse du chantier en 4 champs</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>adresse_numero</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Rens.gen.</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Nr.</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Ajouté : scission adresse du chantier en 4 champs</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>adresse_code_postal</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Rens.gen.</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Code postal</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Postcode</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Ajouté : scission adresse du chantier en 4 champs</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>adresse_ville</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Rens.gen.</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Ville</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Stad</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Ajouté : scission adresse du chantier en 4 champs</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>hopital_code_postal_utilise</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Code postal utilisé pour la recherche : {cp} (depuis l'adresse du chantier)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Postcode used for the search: {cp} (from the site address)</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Postcode gebruikt voor de zoekopdracht: {cp} (van het bouwplaatsadres)</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>Ajouté : recherche hôpitaux basée sur l'adresse</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>hopital_code_postal_manquant</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Renseigne le code postal du chantier dans Renseignements généraux pour lancer la recherche automatique, ou saisis-le ici.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Fill in the site's postcode in General Information to launch the automatic search, or enter it here.</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Vul de postcode van de bouwplaats in bij Algemene Inlichtingen om de automatische zoekopdracht te starten, of voer deze hier in.</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Ajouté : recherche hôpitaux basée sur l'adresse</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>hopital_reutiliser_code_postal</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Infos admin</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Reprendre le code postal du chantier ({cp})</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Reuse the site's postcode ({cp})</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Postcode van de bouwplaats overnemen ({cp})</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>Ajouté : recherche hôpitaux basée sur l'adresse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G320"/>
+  <dimension ref="A1:G322"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11482,6 +11482,80 @@
         </is>
       </c>
     </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>renseignements_titre</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Rens.gen.</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Renseignements</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Inlichtingen</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Ajouté : scission Renseignements Généraux en 2 blocs</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>adresse_chantier_titre</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Rens.gen.</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Adresse chantier</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Site address</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Adres bouwplaats</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Ajouté : scission Renseignements Généraux en 2 blocs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G322"/>
+  <dimension ref="A1:G327"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11556,6 +11556,191 @@
         </is>
       </c>
     </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>niveau_acceptable</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Kinney</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Acceptable</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Aanvaardbaar</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Ajouté : niveauCode langue-indépendant pour la couleur d'évaluation Kinney</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>niveau_attention</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Kinney</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Attention requise</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Attention required</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Aandacht vereist</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Ajouté : niveauCode langue-indépendant pour la couleur d'évaluation Kinney</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>niveau_correction</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Kinney</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Correction nécessaire</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Correction required</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Correctie noodzakelijk</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Ajouté : niveauCode langue-indépendant pour la couleur d'évaluation Kinney</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>niveau_immediate</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Kinney</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Mesure immédiate</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Immediate action</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Onmiddellijke maatregel</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Ajouté : niveauCode langue-indépendant pour la couleur d'évaluation Kinney</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>niveau_arret</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Kinney</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Envisager l'arrêt</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Consider stopping the work</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Stopzetting overwegen</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Ajouté : niveauCode langue-indépendant pour la couleur d'évaluation Kinney</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G327"/>
+  <dimension ref="A1:G332"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11741,6 +11741,191 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>identification_image_page_de_garde_titre</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Image page de garde</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Cover page image</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Afbeelding voorblad</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Ajouté : upload d'une image de couverture propre au chantier</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>identification_image_page_de_garde_texte</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Si vous voulez remplacer l'image générique de la page de garde par votre propre image, téléchargez-la ici.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>If you want to replace the generic cover page image with your own, upload it here.</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Als u de generieke afbeelding op het voorblad wilt vervangen door uw eigen afbeelding, upload deze dan hier.</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Ajouté : upload d'une image de couverture propre au chantier</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>identification_image_page_de_garde_bouton</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Télécharger une image</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Upload an image</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Een afbeelding uploaden</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>Ajouté : upload d'une image de couverture propre au chantier</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>identification_image_page_de_garde_reinitialiser</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Revenir à l'image par défaut</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Revert to the default image</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Terug naar de standaardafbeelding</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>Ajouté : upload d'une image de couverture propre au chantier</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>identification_image_page_de_garde_erreur</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Fichier invalide : utilisez une image PNG ou JPG.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Invalid file: please use a PNG or JPG image.</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Ongeldig bestand: gebruik een PNG- of JPG-afbeelding.</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Ajouté : upload d'une image de couverture propre au chantier</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G332"/>
+  <dimension ref="A1:G333"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11926,6 +11926,43 @@
         </is>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>annexe4_signature_titre</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Annexe 4</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>manuel</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Handtekening</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Ajouté : bloc signature (Operations Manager/Project Manager/Responsable SIPPT) en Annexe 4, remplace l'ancien intitulé 'Avis' du document de référence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G333"/>
+  <dimension ref="A1:G334"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11963,6 +11963,38 @@
         </is>
       </c>
     </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>analyse_tout_cocher</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Analyse de risques</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Tout cocher</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Check all</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Alles aanvinken</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/RePSS_UI_Textes_maitre.xlsx
+++ b/RePSS_UI_Textes_maitre.xlsx
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G334"/>
+  <dimension ref="A1:G404"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11995,6 +11995,2246 @@
         </is>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>gsm</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Générique</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Mobile</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>GSM</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Générique</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>icu_client_titre</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Client (raison sociale)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Client (company name)</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Klant (bedrijfsnaam)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>icu_nom_entreprise</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Nom de l'entreprise</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Company name</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Naam van het bedrijf</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>icu_representant_employeur</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Représentant de l'employeur</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Employer's representative</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Vertegenwoordiger van de werkgever</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>icu_lieu_execution_titre</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Renseignements du lieu d'exécution</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Site information</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Gegevens over de uitvoeringsplaats</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>icu_coactivite_bloquant</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Coactivité : bascule automatiquement ce chantier en RePSS complet.</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Co-activity: automatically switches this site to the full RePSS.</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Co-activiteit: dit werk schakelt automatisch over naar de volledige RePSS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>icu_installation_titre</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Renseignements sur l'installation d'intervention (si usine)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Information on the installation involved (if factory)</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Gegevens over de betrokken installatie (indien fabriek)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>icu_matieres_premieres</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Matières premières mises en œuvre</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Raw materials used</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Gebruikte grondstoffen</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>icu_produits_dangereux</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Produits dangereux utilisés</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Hazardous products used</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Gebruikte gevaarlijke producten</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>icu_description_process</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Description succincte du process</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Brief process description</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Beknopte procesbeschrijving</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>icu_presence_gaz_detail</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Si oui, lequel ?</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>If yes, which one?</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Zo ja, welk?</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>icu_renseignements_generaux_titre</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Renseignements généraux</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>General information</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Algemene gegevens</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>icu_lieu_execution_specifique</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Lieux d'exécution spécifique chez le client</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Specific execution location at the client</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Specifieke uitvoeringslocatie bij de klant</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>icu_mode_operatoire</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Mode opératoire abrégé (nature des travaux)</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Abridged method statement (nature of works)</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Verkorte werkwijze (aard van de werken)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>icu_date_fin_travaux_presumee</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Date présumée de fin des travaux</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Estimated end date of works</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Vermoedelijke einddatum van de werken</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>icu_representant_vma_nom</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Nom du représentant vma sud sur le site</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Name of the vma sud site representative</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Naam van de vma sud vertegenwoordiger ter plaatse</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>icu_regime_travail</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Régime de travail</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Work shift regime</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Werkregime</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>icu_regime_1_poste</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>1 poste</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>1 shift</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>1 ploeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>icu_regime_2_postes</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2 postes</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2 shifts</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>2 ploegen</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>icu_effectif_moyen</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Effectif moyen par poste</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Average headcount per shift</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Gemiddelde bezetting per ploeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>icu_sous_traitants_titre</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Sous-traitants de vma sud</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>vma sud subcontractors</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Onderaannemers van vma sud</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>icu_nom_sous_traitant</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Nom du sous-traitant</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Subcontractor name</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Naam onderaannemer</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>icu_activites_sous_traitant</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Activités du sous-traitant</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Subcontractor activities</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Activiteiten onderaannemer</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>icu_ouverture_chantier</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Existe-t-il une ouverture de chantier réalisée par le client ?</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Has a site opening been carried out by the client?</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Is er een werfopening uitgevoerd door de klant?</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>icu_ouverture_chantier_note</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Si oui, cette ouverture doit être annexée à ce plan sécurité santé et émargée par notre personnel.</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>If yes, this opening must be attached to this health and safety plan and signed off by our staff.</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Zo ja, moet deze opening bij dit veiligheids- en gezondheidsplan gevoegd en door ons personeel geparafeerd worden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>icu_habilitations_titre</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Habilitations</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Qualifications</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Bevoegdheden</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>icu_hab_chariot</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Chariot élévateur</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Forklift</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Vorkheftruck</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>icu_hab_nacelle</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Nacelle</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Aerial work platform</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Hoogwerker</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>icu_hab_pontier</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Pontier</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Crane operator</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Kraanman</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>icu_hab_levage</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Levage, télescopique</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Lifting, telehandler</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Hijsen, verreiker</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>icu_hab_ba4</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>BA4</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>BA4</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>BA4</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>icu_hab_ba5</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>BA5</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>BA5</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>BA5</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>icu_hab_soudeur</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Soudeur</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Welder</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Lasser</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>icu_hab_frigoriste</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Frigoriste</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Refrigeration technician</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Koeltechnicus</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>icu_hab_autre</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Autre</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Andere</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>icu_hab_autre_ajouter</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Ajouter une habilitation</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Add a qualification</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Bevoegdheid toevoegen</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>icu_locaux_sociaux_titre</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Locaux sociaux et installation de chantier (nettoyage compris)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>Welfare facilities and site installation (cleaning included)</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Sociale voorzieningen en werfinstallatie (reiniging inbegrepen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>icu_engins_disposition</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Engins, appareils ou outillages mis à disposition par le client ?</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Equipment, machinery or tools provided by the client?</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Machines, toestellen of gereedschap ter beschikking gesteld door de klant?</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>icu_engins_disposition_detail</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Si oui, le(s)quel(s) ?</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>If yes, which one(s)?</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Zo ja, welke?</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>icu_epi_titre</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Équipements de protection individuelle</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Personal protective equipment</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Persoonlijke beschermingsmiddelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>icu_epi_casque</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Casque</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Helmet</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Helm</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>icu_epi_chaussures</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Chaussures de sécurité</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Safety shoes</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Veiligheidsschoenen</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>icu_epi_lunettes</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Lunettes</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Goggles</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Bril</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>icu_epi_gants_combinaison</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Gants / combinaison</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Gloves / coveralls</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Handschoenen / overall</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>icu_epi_protection_auditive</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Protection auditive</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Hearing protection</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Gehoorbescherming</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>icu_epi_masque_anti_poussiere</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Masque anti-poussière</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Dust mask</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Stofmasker</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>icu_epi_protection_faciale</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Protection faciale</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Face protection</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Gelaatsbescherming</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>icu_epi_harnais</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Harnais de sécurité</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Safety harness</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Veiligheidsharnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>icu_epi_autres</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Autres</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Andere</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>icu_protection_env_titre</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Protection pour l'environnement</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Environmental protection</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Milieubescherming</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>icu_evacuation_dechets</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Évacuation des déchets</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>Waste disposal</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Afvalverwijdering</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>icu_evacuation_gaz</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Évacuation des gaz frigorifiques</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Refrigerant gas disposal</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Afvoer van koelgassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>icu_permis_titre</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Mesures générales de sécurité</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>General safety measures</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Algemene veiligheidsmaatregelen</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>icu_permis_travail_obligatoire</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Permis de travail obligatoire</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Work permit mandatory</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Werkvergunning verplicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>icu_consignation_installations</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Consignation des installations</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Lock-out of installations</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Vergrendeling van installaties</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>icu_permis_espace_restreint</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Permis, espace restreint</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Confined space permit</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Vergunning besloten ruimte</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>icu_permis_fouille</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Permis de fouille, ouverture plancher</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Excavation / floor opening permit</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Vergunning graafwerk, vloeropening</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>icu_permis_feu</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Permis de feu</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Hot work permit</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Vuurvergunning</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>icu_mode_operatoire_execution</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Mode opératoire d'exécution</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Execution method statement</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Uitvoeringswerkwijze</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>icu_organisation_secours_titre</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Organisation des secours</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Emergency organisation</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Organisatie van de hulpverlening</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>icu_numero_urgence_interne</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Numéro d'appel d'urgence interne (Client)</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Internal emergency number (Client)</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Intern noodnummer (Klant)</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>icu_infirmerie</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Infirmerie</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Infirmary</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Ziekenboeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>icu_service_securite</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Service sécurité</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Security service</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Veiligheidsdienst</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>icu_pompiers</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Pompiers</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Fire brigade</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Brandweer</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>icu_gardiennage</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Gardiennage</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Security guard</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Bewaking</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>icu_approbation_titre</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Approbation de la Réponse au Plan Sécurité Santé abrégé</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Approval of the abridged Health &amp; Safety Plan Response</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Goedkeuring van het verkorte Antwoord op het Veiligheids- en Gezondheidsplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>icu_approbation_vma_responsable</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>vma sud : Nom du responsable</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>vma sud: Manager's name</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>vma sud: Naam verantwoordelijke</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>icu_approbation_vma_conseiller</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>vma sud : Nom du Conseiller en Prévention</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>vma sud: Name of the Prevention Advisor</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>vma sud: Naam van de Preventieadviseur</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>icu_approbation_client_responsable</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Infos chantier &amp; usine (abrégé)</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>n/a (nouveau)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Client : Nom du responsable</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Client: Manager's name</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Klant: Naam verantwoordelijke</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
